--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ServiceEvent représente un évènement (acte, traitement, diagnostic, etc…) décrit dans le document. 
+    <t>L'élément de l'en-tête du CDA serviceEvent permet de représenter un évènement (acte, traitement, diagnostic, etc…) décrit dans le document. 
 L'occurrence de documentationOf/serviceEvent contenant les données de l’évènement documenté principal doit inclure un élément effectiveTime et un élément performer renseignés, sans recours à l'attribut nullFlavor.</t>
   </si>
   <si>
@@ -853,7 +853,40 @@
     <t>ServiceEvent.performer.assignedEntity.id</t>
   </si>
   <si>
+    <t>Identifiant du responsable</t>
+  </si>
+  <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>ServiceEvent.performer.assignedEntity.sdtcIdentifiedBy</t>
@@ -869,6 +902,9 @@
     <t>ServiceEvent.performer.assignedEntity.code</t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -915,6 +951,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -925,6 +964,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -935,6 +977,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -943,6 +992,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -1263,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK89"/>
+  <dimension ref="A1:AK94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
@@ -6032,7 +6086,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -8377,7 +8431,9 @@
       <c r="K70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L70" s="2"/>
+      <c r="L70" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8428,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8448,16 +8504,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
@@ -8474,10 +8532,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>268</v>
+        <v>86</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8503,13 +8563,11 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8527,13 +8585,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>90</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8547,21 +8605,23 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8573,10 +8633,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8602,11 +8664,13 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>271</v>
+        <v>74</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8624,7 +8688,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8644,17 +8708,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -8672,11 +8736,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8703,11 +8767,13 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8725,7 +8791,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8745,20 +8811,20 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>75</v>
@@ -8773,11 +8839,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="M74" t="s" s="2">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8828,7 +8896,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8848,20 +8916,20 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
@@ -8876,11 +8944,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L75" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="M75" t="s" s="2">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -8931,7 +9001,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8960,14 +9030,12 @@
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -8979,12 +9047,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9034,13 +9100,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9054,23 +9120,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9082,12 +9146,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L77" s="2"/>
-      <c r="M77" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9113,13 +9177,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>74</v>
+        <v>281</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9137,7 +9199,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>151</v>
+        <v>282</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9157,23 +9219,23 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9185,11 +9247,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9216,13 +9278,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9240,7 +9300,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9260,21 +9320,23 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9286,11 +9348,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9341,7 +9403,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9361,21 +9423,23 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9387,11 +9451,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9442,7 +9506,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9462,17 +9526,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9490,11 +9554,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9545,7 +9609,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9565,17 +9629,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9593,11 +9657,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9648,13 +9712,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9668,23 +9732,23 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9696,11 +9760,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9751,13 +9815,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9771,10 +9835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9785,7 +9849,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9797,10 +9861,12 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>285</v>
+        <v>157</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9850,13 +9916,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>286</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9870,10 +9936,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9884,7 +9950,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -9896,10 +9962,12 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>288</v>
+        <v>102</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -9949,13 +10017,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -9969,16 +10037,18 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
@@ -9995,10 +10065,12 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10048,7 +10120,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>292</v>
+        <v>167</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10068,21 +10140,23 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10094,10 +10168,12 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>294</v>
+        <v>170</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10147,13 +10223,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>295</v>
+        <v>172</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10167,21 +10243,23 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10193,10 +10271,12 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>175</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10246,13 +10326,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>298</v>
+        <v>178</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10266,10 +10346,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10277,10 +10357,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10292,9 +10372,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L89" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10345,21 +10427,522 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK89" t="s" s="2">
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
 - Pour un document au format CDA R2 N3, se reporter au volet de contenus correspondant.
 - Pour certains documents au format CDA R2 N1, la valeur est fixée (voir tableau qui suit).
 - Dans les autres cas, utiliser une valeur issue d'une terminologie internationale (ex : CIM10 pour les actes) ou nationale (ex : CCAM pour les actes).
-Pour les documents d’expression personnelle du patient/usager :
+- Pour les documents d’expression personnelle du patient/usager :
 - valeur fixée</t>
   </si>
   <si>
